--- a/用户导入测试.xlsx
+++ b/用户导入测试.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\taikao-test\TaiKao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737218F9-6119-43C2-97ED-52CBD463224D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067A3163-2CC5-41F1-9E71-3E579BFAFFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-408" yWindow="1236" windowWidth="18252" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>用户名</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -60,6 +60,39 @@
   <si>
     <t>102046017@qq.com</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户姓名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>张三</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李四</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>王五</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认密码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级管理员</t>
+  </si>
+  <si>
+    <t>用户角色（“超级管理员”、“教师”、“普通用户”）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教师</t>
+  </si>
+  <si>
+    <t>普通用户</t>
   </si>
 </sst>
 </file>
@@ -134,12 +167,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -445,75 +483,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="5" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="60.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2">
+        <v>123456</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="E2" s="2">
         <v>2312312</v>
       </c>
-      <c r="D2">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2">
+        <v>123456</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="E3" s="2">
         <v>205464878</v>
       </c>
-      <c r="D3">
+      <c r="F3" s="2">
         <v>1</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2">
+        <v>123456</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="E4" s="2">
         <v>1234678</v>
       </c>
-      <c r="D4">
+      <c r="F4" s="2">
         <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{EAF64B9D-D7D0-44CF-BB68-2BAD4A5B6412}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{511513C5-2840-44BE-933A-C9C2F44DF51B}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{6953AB35-1982-434B-B3FE-17470AC6BECE}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{EAF64B9D-D7D0-44CF-BB68-2BAD4A5B6412}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{511513C5-2840-44BE-933A-C9C2F44DF51B}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{6953AB35-1982-434B-B3FE-17470AC6BECE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>